--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486505_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486505_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.285299999999999</v>
+        <v>8.970499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2831</v>
+        <v>8.2456</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0022</v>
+        <v>0.7248</v>
       </c>
       <c r="G2" t="n">
         <v>4.6451</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2705</v>
+        <v>0.9556</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6934</v>
+        <v>0.2692</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9639</v>
+        <v>0.6865</v>
       </c>
       <c r="V2" t="n">
         <v>2.0647</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6395</v>
+        <v>2.0533</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9394</v>
+        <v>1.1977</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7001</v>
+        <v>0.8556</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6938</v>
+        <v>3.2304</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9550999999999999</v>
+        <v>1.3076</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2614</v>
+        <v>1.9228</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2899</v>
+        <v>2.1747</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2134</v>
+        <v>0.9125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0765</v>
+        <v>1.2622</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4038</v>
+        <v>1.0557</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7417</v>
+        <v>0.3951</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3379</v>
+        <v>0.6606</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7081</v>
+        <v>0.1703</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7169</v>
+        <v>0.1106</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9913</v>
+        <v>0.0598</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.246</v>
+        <v>1.2119</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4212</v>
+        <v>-0.6669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8247</v>
+        <v>1.8788</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2304</v>
+        <v>-1.969</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3076</v>
+        <v>0.6264</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9228</v>
+        <v>-2.5954</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1747</v>
+        <v>-1.3098</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9125</v>
+        <v>-0.4134</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2622</v>
+        <v>-0.8964</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0557</v>
+        <v>-0.6592</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3951</v>
+        <v>1.0398</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6606</v>
+        <v>-1.6989</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>2.6101</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>0.363</v>
+        <v>0.5708</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3341</v>
+        <v>0.6429</v>
       </c>
       <c r="U4" t="n">
-        <v>0.029</v>
+        <v>-0.0721</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8593</v>
+        <v>1.1994</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8255</v>
+        <v>-0.1118</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0337</v>
+        <v>1.3111</v>
       </c>
       <c r="G5" t="n">
         <v>0.5286999999999999</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5056</v>
+        <v>0.8457</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2077</v>
+        <v>0.2704</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2979</v>
+        <v>0.5753</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8536</v>
+        <v>-0.0169</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7786999999999999</v>
+        <v>0.4769</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6322</v>
+        <v>-0.4938</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.969</v>
+        <v>-0.1145</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6264</v>
+        <v>-0.0882</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.5954</v>
+        <v>-0.0263</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3098</v>
+        <v>0.7509</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4134</v>
+        <v>0.3102</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8964</v>
+        <v>0.4407</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6592</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0398</v>
+        <v>-0.3985</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6989</v>
+        <v>-0.467</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6101</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6101</v>
+        <v>0.2175</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2125</v>
+        <v>-0.1199</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5312</v>
+        <v>-0.274</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3187</v>
+        <v>0.1541</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1094</v>
+        <v>-0.2232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4769</v>
+        <v>-2.4904</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5863</v>
+        <v>2.2672</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1145</v>
+        <v>-0.6924</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0882</v>
+        <v>0.9547</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0263</v>
+        <v>-1.6471</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7509</v>
+        <v>-2.0127</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3102</v>
+        <v>0.146</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4407</v>
+        <v>-2.1587</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8653999999999999</v>
+        <v>1.3203</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3985</v>
+        <v>0.8087</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.467</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2123</v>
+        <v>0.709</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.274</v>
+        <v>0.4146</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0616</v>
+        <v>0.2944</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2405</v>
+        <v>-0.3445</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3845</v>
+        <v>-0.9829</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1439</v>
+        <v>0.6385</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6924</v>
+        <v>-0.8948</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9547</v>
+        <v>0.903</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6471</v>
+        <v>-1.7977</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0127</v>
+        <v>0.2649</v>
       </c>
       <c r="K8" t="n">
-        <v>0.146</v>
+        <v>0.4927</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.1587</v>
+        <v>-0.2279</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3203</v>
+        <v>-1.1596</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8087</v>
+        <v>0.4102</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5116000000000001</v>
+        <v>-1.5698</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.435</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3084</v>
+        <v>0.4431</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4795</v>
+        <v>-0.2451</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1711</v>
+        <v>0.6883</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>2.0647</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4727</v>
+        <v>-0.4664</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8337</v>
+        <v>-1.5193</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3611</v>
+        <v>1.0529</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8948</v>
+        <v>0.6938</v>
       </c>
       <c r="H9" t="n">
-        <v>0.903</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7977</v>
+        <v>-0.2614</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2649</v>
+        <v>0.2899</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4927</v>
+        <v>0.2134</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2279</v>
+        <v>0.0765</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1596</v>
+        <v>0.4038</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4102</v>
+        <v>0.7417</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5698</v>
+        <v>-0.3379</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9576</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q9" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6851</v>
+        <v>1.6022</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0959</v>
+        <v>1.2582</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4108</v>
+        <v>0.344</v>
       </c>
       <c r="V9" t="n">
-        <v>2.0647</v>
+        <v>-0.3698</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2599</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1014</v>
+        <v>-1.7661</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3539</v>
+        <v>-2.0186</v>
       </c>
       <c r="F10" t="n">
         <v>0.2525</v>
@@ -1234,10 +1234,10 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.435</v>
+        <v>-0.0997</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.137</v>
+        <v>0.1983</v>
       </c>
       <c r="U10" t="n">
         <v>-0.298</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6943</v>
+        <v>-3.1225</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2364</v>
+        <v>-3.0207</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4579</v>
+        <v>-0.1018</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0195</v>
+        <v>-2.7288</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2341</v>
+        <v>0.3439</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2536</v>
+        <v>-3.0727</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4536</v>
+        <v>-0.9348</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0365</v>
+        <v>-0.346</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4901</v>
+        <v>-0.5888</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5659</v>
+        <v>-1.794</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1976</v>
+        <v>0.6899</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7635</v>
+        <v>-2.4838</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>0.435</v>
+        <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>0.87</v>
+        <v>-0.0463</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1971</v>
+        <v>-0.4759</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.4296</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.27</v>
+        <v>-4.1575</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9833</v>
+        <v>-3.3914</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2867</v>
+        <v>-0.7662</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7288</v>
+        <v>-3.0195</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3439</v>
+        <v>0.2341</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0727</v>
+        <v>-3.2536</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9348</v>
+        <v>-1.4536</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.346</v>
+        <v>0.0365</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5888</v>
+        <v>-1.4901</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.794</v>
+        <v>-1.5659</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6899</v>
+        <v>0.1976</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.4838</v>
+        <v>-1.7635</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2175</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3926</v>
+        <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1938</v>
+        <v>0.4068</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4384</v>
+        <v>0.0421</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2447</v>
+        <v>0.3647</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9954</v>
+        <v>3.337999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6244</v>
+        <v>-4.281800000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>7.6195</v>
+        <v>7.619599999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.422399999999999</v>
+        <v>-2.4224</v>
       </c>
       <c r="H13" t="n">
         <v>9.275599999999997</v>
@@ -1459,7 +1459,7 @@
         <v>-9.4389</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.2627</v>
+        <v>-3.262700000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.4005</v>
@@ -1468,28 +1468,28 @@
         <v>14.1379</v>
       </c>
       <c r="S13" t="n">
-        <v>5.0951</v>
+        <v>5.4376</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8688</v>
+        <v>2.2113</v>
       </c>
       <c r="U13" t="n">
-        <v>3.226500000000001</v>
+        <v>3.226599999999999</v>
       </c>
       <c r="V13" t="n">
         <v>3.585</v>
       </c>
       <c r="W13" t="n">
-        <v>8.4954</v>
+        <v>8.495399999999998</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.910399999999999</v>
+        <v>-4.9104</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>J. BONE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.03</v>
+        <v>4.5131</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1368</v>
+        <v>2.6728</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1068</v>
+        <v>1.8403</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6683</v>
+        <v>2.8163</v>
       </c>
       <c r="H14" t="n">
-        <v>0.222</v>
+        <v>-1.6851</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4463</v>
+        <v>4.5015</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4566</v>
+        <v>3.2604</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9704</v>
+        <v>-1.2164</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4862</v>
+        <v>4.4768</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7882</v>
+        <v>-0.4441</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7484</v>
+        <v>-0.4688</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0399</v>
+        <v>0.0247</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6525</v>
+        <v>2.3926</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6525</v>
+        <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7091</v>
+        <v>-0.6958</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6802</v>
+        <v>-0.5876</v>
       </c>
       <c r="U14" t="n">
-        <v>0.029</v>
+        <v>-0.1082</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BONE</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6075</v>
+        <v>3.2785</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8905</v>
+        <v>3.3545</v>
       </c>
       <c r="F15" t="n">
-        <v>1.717</v>
+        <v>-0.0759</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8163</v>
+        <v>2.6683</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6851</v>
+        <v>0.222</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5015</v>
+        <v>2.4463</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2604</v>
+        <v>3.4566</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2164</v>
+        <v>0.9704</v>
       </c>
       <c r="L15" t="n">
-        <v>4.4768</v>
+        <v>2.4862</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4441</v>
+        <v>-0.7882</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4688</v>
+        <v>-0.7484</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0247</v>
+        <v>-0.0399</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6014</v>
+        <v>-0.0424</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3699</v>
+        <v>-0.1021</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2315</v>
+        <v>0.0598</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5788</v>
+        <v>2.7214</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7015</v>
+        <v>0.8133</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8773</v>
+        <v>1.9081</v>
       </c>
       <c r="G16" t="n">
         <v>4.1493</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.918</v>
+        <v>-0.7754</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3509</v>
+        <v>-0.2391</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5671</v>
+        <v>-0.5363</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>M. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7567</v>
+        <v>0.2556</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3146</v>
+        <v>-1.5575</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0713</v>
+        <v>1.8131</v>
       </c>
       <c r="G17" t="n">
-        <v>1.753</v>
+        <v>0.8919</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2286</v>
+        <v>0.6481</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5244</v>
+        <v>0.2438</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.771</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0326</v>
+        <v>1.3814</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6702</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1154</v>
+        <v>0.1209</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2612</v>
+        <v>-0.7333</v>
       </c>
       <c r="O17" t="n">
         <v>0.8542</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>2.8276</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7209</v>
+        <v>-1.2888</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4627</v>
+        <v>-1.2834</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2582</v>
+        <v>-0.0054</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4997</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7602</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.578</v>
+        <v>-0.0294</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0055</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5834</v>
+        <v>0.7322</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0748</v>
+        <v>1.753</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7577</v>
+        <v>0.2286</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6829</v>
+        <v>1.5244</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3806</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5719</v>
+        <v>-0.0326</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1912</v>
+        <v>0.6702</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3058</v>
+        <v>1.1154</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1858</v>
+        <v>0.2612</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4916</v>
+        <v>0.8542</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7401</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8276</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1079</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4627</v>
+        <v>0.0156</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3548</v>
+        <v>-0.0808</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1952</v>
+        <v>-1.4997</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. TORRES CUEVAS</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.0425</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.781</v>
+        <v>-2.5643</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8747</v>
+        <v>2.5218</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8919</v>
+        <v>-1.0748</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6481</v>
+        <v>-1.7577</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2438</v>
+        <v>0.6829</v>
       </c>
       <c r="J19" t="n">
-        <v>0.771</v>
+        <v>-1.3806</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3814</v>
+        <v>-1.5719</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.1912</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1209</v>
+        <v>0.3058</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7333</v>
+        <v>-0.1858</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8542</v>
+        <v>0.4916</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
         <v>2.8276</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4507</v>
+        <v>-0.5125</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5069</v>
+        <v>-0.0961</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0562</v>
+        <v>-0.4164</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2379</v>
+        <v>-0.0453</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1242</v>
+        <v>0.3477</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3621</v>
+        <v>-0.3929</v>
       </c>
       <c r="G20" t="n">
         <v>-0.894</v>
@@ -2014,13 +2014,13 @@
         <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8665</v>
+        <v>-0.6738</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8904</v>
+        <v>-0.6669</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0239</v>
+        <v>-0.0069</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1467</v>
+        <v>-1.1159</v>
       </c>
       <c r="E21" t="n">
         <v>-0.9385</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2082</v>
+        <v>-0.1773</v>
       </c>
       <c r="G21" t="n">
         <v>0.1155</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="T21" t="n">
         <v>0.149</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6312</v>
+        <v>-1.4077</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0529</v>
+        <v>-0.8294</v>
       </c>
       <c r="F22" t="n">
         <v>-0.5783</v>
@@ -2170,10 +2170,10 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.721</v>
+        <v>-0.4975</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4675</v>
+        <v>-0.2439</v>
       </c>
       <c r="U22" t="n">
         <v>-0.2536</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0128</v>
+        <v>-2.845</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1577</v>
+        <v>-3.2029</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8552</v>
+        <v>0.3579</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6776</v>
+        <v>-1.542</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3285</v>
+        <v>-1.7213</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3491</v>
+        <v>0.1793</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6097</v>
+        <v>-2.1022</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3436</v>
+        <v>-1.4719</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2661</v>
+        <v>-0.6303</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0679</v>
+        <v>0.5601</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0151</v>
+        <v>-0.2495</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0829</v>
+        <v>0.8096</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2929</v>
+        <v>-0.4329</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.548</v>
+        <v>-0.0132</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2551</v>
+        <v>-0.4197</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1108</v>
+        <v>-2.9204</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3147</v>
+        <v>-1.1577</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2038</v>
+        <v>-1.7627</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.542</v>
+        <v>-1.6776</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7213</v>
+        <v>-0.3285</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1793</v>
+        <v>-1.3491</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1022</v>
+        <v>-0.6097</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4719</v>
+        <v>-0.3436</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6303</v>
+        <v>-0.2661</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5601</v>
+        <v>-1.0679</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2495</v>
+        <v>0.0151</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8096</v>
+        <v>-1.0829</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6988</v>
+        <v>-0.2004</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.125</v>
+        <v>-0.548</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5738</v>
+        <v>0.3476</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5005</v>
+        <v>-5.3579</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9078</v>
+        <v>-3.796</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5928</v>
+        <v>-1.5619</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1335</v>
@@ -2404,13 +2404,13 @@
         <v>1.0875</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1044</v>
+        <v>0.0382</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2776</v>
+        <v>0.3894</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.382</v>
+        <v>-0.3512</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.995199999999998</v>
+        <v>-2.995500000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.6197</v>
+        <v>-7.6196</v>
       </c>
       <c r="F26" t="n">
-        <v>4.6241</v>
+        <v>4.6244</v>
       </c>
       <c r="G26" t="n">
-        <v>2.422100000000002</v>
+        <v>2.4221</v>
       </c>
       <c r="H26" t="n">
         <v>-9.275600000000001</v>
@@ -2458,13 +2458,13 @@
         <v>4.8344</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.604799999999999</v>
+        <v>-4.6048</v>
       </c>
       <c r="L26" t="n">
         <v>9.4389</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.412199999999999</v>
+        <v>-2.4122</v>
       </c>
       <c r="N26" t="n">
         <v>-4.6711</v>
@@ -2473,7 +2473,7 @@
         <v>2.258999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>3.262699999999999</v>
+        <v>3.2627</v>
       </c>
       <c r="Q26" t="n">
         <v>-14.1379</v>
@@ -2482,13 +2482,13 @@
         <v>17.4005</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.095300000000001</v>
+        <v>-5.0951</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.2264</v>
+        <v>-3.2263</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.8689</v>
+        <v>-1.8687</v>
       </c>
       <c r="V26" t="n">
         <v>-3.5851</v>
